--- a/収益物件_返済比率比較_全8件_2026-06-27.xlsx
+++ b/収益物件_返済比率比較_全8件_2026-06-27.xlsx
@@ -8,7 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="返済比率・CF比較" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="前提条件" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="⑤購入スキーム" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="前提条件" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +22,7 @@
     <numFmt numFmtId="164" formatCode="0.0&quot;%&quot;"/>
     <numFmt numFmtId="165" formatCode="0.00&quot;%&quot;"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,8 +43,21 @@
       <b val="1"/>
       <sz val="12"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F4E78"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -58,6 +72,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -87,7 +106,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -126,6 +145,34 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1215,6 +1262,470 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>⑤ プレ・ラグーナ 購入スキーム整理（滋賀銀行／セゾン保証・オーバーローン）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>物件・売主</t>
+        </is>
+      </c>
+      <c r="B3" s="16" t="n"/>
+      <c r="C3" s="16" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>物件名</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>プレ・ラグーナ（一棟アパート）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="17" t="inlineStr">
+        <is>
+          <t>所在地</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>岐阜県瑞浪市南小田町4丁目110</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t>売主／担当</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>A-NEXT株式会社／本間 氏</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>構造・戸数</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>木造2階建・全10戸（1K×5/1LDK×5）・築24年(2003/3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t>物件価格(円)</t>
+        </is>
+      </c>
+      <c r="B8" s="18" t="n">
+        <v>53100000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t>諸費用(円)※火災保険35万含む</t>
+        </is>
+      </c>
+      <c r="B9" s="18" t="n">
+        <v>1400000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>申込先</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>滋賀銀行（保証：セゾンファンデックス）／申込予定 2026-06-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>資金計画（借入構成）</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="n"/>
+      <c r="C12" s="16" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>商品 / 内訳</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>借入額(円)</t>
+        </is>
+      </c>
+      <c r="C13" s="19" t="inlineStr">
+        <is>
+          <t>期間</t>
+        </is>
+      </c>
+      <c r="D13" s="19" t="inlineStr">
+        <is>
+          <t>金利</t>
+        </is>
+      </c>
+      <c r="E13" s="19" t="inlineStr">
+        <is>
+          <t>月返済(円)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="20" t="inlineStr">
+        <is>
+          <t>アパートローン（有担保3500万+属性優遇1000万）</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="n">
+        <v>45000000</v>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>31年(※30年要確認)</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>2.8%(※要確認)</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="n">
+        <v>181102</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="20" t="inlineStr">
+        <is>
+          <t>無担保ローン（810万 物件+140万 諸費用+250万 運転資金）</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>20年</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>3.25%</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="n">
+        <v>68063</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="23" t="inlineStr">
+        <is>
+          <t>借入合計（＝オーバーローン）</t>
+        </is>
+      </c>
+      <c r="B16" s="24" t="n">
+        <v>57000000</v>
+      </c>
+      <c r="C16" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D16" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E16" s="24" t="n">
+        <v>249165</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>資金使途（オーバーローンの内訳）</t>
+        </is>
+      </c>
+      <c r="B18" s="16" t="n"/>
+      <c r="C18" s="16" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>物件価格(円)</t>
+        </is>
+      </c>
+      <c r="B19" s="18" t="n">
+        <v>53100000</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>諸費用(円)</t>
+        </is>
+      </c>
+      <c r="B20" s="18" t="n">
+        <v>1400000</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="17" t="inlineStr">
+        <is>
+          <t>手元運転資金＝後日キャッシュバック(円)</t>
+        </is>
+      </c>
+      <c r="B21" s="26" t="n">
+        <v>2500000</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="17" t="inlineStr">
+        <is>
+          <t>合計(円)＝借入合計</t>
+        </is>
+      </c>
+      <c r="B22" s="18" t="n">
+        <v>57000000</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="17" t="inlineStr">
+        <is>
+          <t>LTV（借入÷物件価格）</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="inlineStr">
+        <is>
+          <t>107.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>収益・キャッシュフロー（満室＝現況：満室稼働）</t>
+        </is>
+      </c>
+      <c r="B25" s="16" t="n"/>
+      <c r="C25" s="16" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="17" t="inlineStr">
+        <is>
+          <t>満室月収入(円)〔賃料416,000+共益17,000+駐車29,700〕</t>
+        </is>
+      </c>
+      <c r="B26" s="18" t="n">
+        <v>462700</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="17" t="inlineStr">
+        <is>
+          <t>満室年収入(円)</t>
+        </is>
+      </c>
+      <c r="B27" s="18" t="n">
+        <v>5552400</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="17" t="inlineStr">
+        <is>
+          <t>運営費 ランニングコスト(円/月)〔賃料の約18.5%〕</t>
+        </is>
+      </c>
+      <c r="B28" s="18" t="n">
+        <v>85842</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="17" t="inlineStr">
+        <is>
+          <t>NOI 家賃収入小計(円/月)</t>
+        </is>
+      </c>
+      <c r="B29" s="18" t="n">
+        <v>376858</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="17" t="inlineStr">
+        <is>
+          <t>月返済合計(円)〔PLAN I〕</t>
+        </is>
+      </c>
+      <c r="B30" s="18" t="n">
+        <v>249165</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="17" t="inlineStr">
+        <is>
+          <t>月CF(円)〔PLAN I・満室=現況〕</t>
+        </is>
+      </c>
+      <c r="B31" s="18" t="n">
+        <v>127693</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="17" t="inlineStr">
+        <is>
+          <t>年CF(円)</t>
+        </is>
+      </c>
+      <c r="B32" s="18" t="n">
+        <v>1532316</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="15" t="inlineStr">
+        <is>
+          <t>指標</t>
+        </is>
+      </c>
+      <c r="B34" s="16" t="n"/>
+      <c r="C34" s="16" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="17" t="inlineStr">
+        <is>
+          <t>表面利回り（対物件価格）</t>
+        </is>
+      </c>
+      <c r="B35" s="17" t="inlineStr">
+        <is>
+          <t>10.46%</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="17" t="inlineStr">
+        <is>
+          <t>返済比率（対満室総収入462,700）</t>
+        </is>
+      </c>
+      <c r="B36" s="27" t="inlineStr">
+        <is>
+          <t>53.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　└運転資金250万分を除く実質返済比率</t>
+        </is>
+      </c>
+      <c r="B37" s="17" t="inlineStr">
+        <is>
+          <t>約50.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="17" t="inlineStr">
+        <is>
+          <t>自己資金</t>
+        </is>
+      </c>
+      <c r="B38" s="17" t="inlineStr">
+        <is>
+          <t>実質ゼロ（むしろ手元+250万）</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="17" t="inlineStr">
+        <is>
+          <t>実質利回り（NOI÷物件価格）</t>
+        </is>
+      </c>
+      <c r="B39" s="17" t="inlineStr">
+        <is>
+          <t>8.52%</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="15" t="inlineStr">
+        <is>
+          <t>参考：売主CF表 PLAN比較</t>
+        </is>
+      </c>
+      <c r="B41" s="16" t="n"/>
+      <c r="C41" s="16" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="17" t="inlineStr">
+        <is>
+          <t>PLAN I（アパート31年2.8%＋無担保20年3.25%）</t>
+        </is>
+      </c>
+      <c r="B42" s="17" t="inlineStr">
+        <is>
+          <t>月CF +127,693円</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="17" t="inlineStr">
+        <is>
+          <t>PLAN II（アパート35年4.025%＋無担保20年3.25%）</t>
+        </is>
+      </c>
+      <c r="B43" s="17" t="inlineStr">
+        <is>
+          <t>月CF +108,871円</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:A15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/収益物件_返済比率比較_全8件_2026-06-27.xlsx
+++ b/収益物件_返済比率比較_全8件_2026-06-27.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="返済比率・CF比較" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="⑤購入スキーム" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="前提条件" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="返済比率・CF比較" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⑤購入スキーム" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="融資申込チェックリスト" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="前提条件" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +23,7 @@
     <numFmt numFmtId="164" formatCode="0.0&quot;%&quot;"/>
     <numFmt numFmtId="165" formatCode="0.00&quot;%&quot;"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -55,6 +56,20 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F4E78"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00808080"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="5">
@@ -106,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -173,6 +188,21 @@
     </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1726,6 +1756,282 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>融資申込前チェックリスト（⑤プレ・ラグーナ／滋賀銀行・セゾン保証）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="29" t="inlineStr">
+        <is>
+          <t>作成日：2026年7月12日</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="30" t="inlineStr">
+        <is>
+          <t>済</t>
+        </is>
+      </c>
+      <c r="B4" s="30" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="C4" s="30" t="inlineStr">
+        <is>
+          <t>確認項目</t>
+        </is>
+      </c>
+      <c r="D4" s="30" t="inlineStr">
+        <is>
+          <t>懸案内容・確認事項</t>
+        </is>
+      </c>
+      <c r="E4" s="30" t="inlineStr">
+        <is>
+          <t>結果／メモ</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="48" customHeight="1">
+      <c r="A5" s="31" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B5" s="31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C5" s="32" t="inlineStr">
+        <is>
+          <t>資金使途</t>
+        </is>
+      </c>
+      <c r="D5" s="33" t="inlineStr">
+        <is>
+          <t>無担保枠1,200万のうち250万を「覚書で後日キャッシュバック」する構図。売主からの価格水増し還流であれば資金使途違反・一括返済請求リスク。誰が・どの名目で返すのか要明確化。</t>
+        </is>
+      </c>
+      <c r="E5" s="17" t="inlineStr"/>
+    </row>
+    <row r="6" ht="48" customHeight="1">
+      <c r="A6" s="31" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B6" s="31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C6" s="32" t="inlineStr">
+        <is>
+          <t>融資期間</t>
+        </is>
+      </c>
+      <c r="D6" s="33" t="inlineStr">
+        <is>
+          <t>完済年齢満81歳ルール。現在51歳(4/21生)→30年が原則。31年だと完済82歳で上限超過の可能性。申込時に確定要。</t>
+        </is>
+      </c>
+      <c r="E6" s="17" t="inlineStr"/>
+    </row>
+    <row r="7" ht="48" customHeight="1">
+      <c r="A7" s="31" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B7" s="31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C7" s="32" t="inlineStr">
+        <is>
+          <t>金利・優遇</t>
+        </is>
+      </c>
+      <c r="D7" s="33" t="inlineStr">
+        <is>
+          <t>比較検討時は2.6%前提だったが、売主CF表はアパート2.8%・無担保3.25%(優遇・団信未加味)。実行金利・優遇幅を要確認。</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="inlineStr"/>
+    </row>
+    <row r="8" ht="48" customHeight="1">
+      <c r="A8" s="31" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B8" s="31" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C8" s="32" t="inlineStr">
+        <is>
+          <t>団体信用生命保険</t>
+        </is>
+      </c>
+      <c r="D8" s="33" t="inlineStr">
+        <is>
+          <t>31年(完済82歳)だと一般団信の年齢上限に抵触の恐れ。ワイド団信/上乗せ/無団信の選択肢と健康告知を確認。</t>
+        </is>
+      </c>
+      <c r="E8" s="17" t="inlineStr"/>
+    </row>
+    <row r="9" ht="48" customHeight="1">
+      <c r="A9" s="31" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B9" s="31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C9" s="32" t="inlineStr">
+        <is>
+          <t>返済比率</t>
+        </is>
+      </c>
+      <c r="D9" s="33" t="inlineStr">
+        <is>
+          <t>無担保分を含めた実際の返済比率は約53.9%(満室)。運転資金250万分を除いても約50.8%。想定より重い。</t>
+        </is>
+      </c>
+      <c r="E9" s="17" t="inlineStr"/>
+    </row>
+    <row r="10" ht="48" customHeight="1">
+      <c r="A10" s="31" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B10" s="31" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C10" s="32" t="inlineStr">
+        <is>
+          <t>無担保枠の余力</t>
+        </is>
+      </c>
+      <c r="D10" s="33" t="inlineStr">
+        <is>
+          <t>属性枠1,200万を全消化するため、次物件・急な資金需要への無担保余力がゼロになる。</t>
+        </is>
+      </c>
+      <c r="E10" s="17" t="inlineStr"/>
+    </row>
+    <row r="11" ht="48" customHeight="1">
+      <c r="A11" s="31" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B11" s="31" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C11" s="32" t="inlineStr">
+        <is>
+          <t>諸費用の内訳</t>
+        </is>
+      </c>
+      <c r="D11" s="33" t="inlineStr">
+        <is>
+          <t>140万円(火災保険35万含む)の内訳確認。登記・司法書士・ローン事務手数料・保証料。不動産取得税(後日課税)が含まれるか要確認。</t>
+        </is>
+      </c>
+      <c r="E11" s="17" t="inlineStr"/>
+    </row>
+    <row r="12" ht="48" customHeight="1">
+      <c r="A12" s="31" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B12" s="31" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C12" s="32" t="inlineStr">
+        <is>
+          <t>物件固有リスク</t>
+        </is>
+      </c>
+      <c r="D12" s="33" t="inlineStr">
+        <is>
+          <t>用途地域=工業地域。土地積算34.9%で担保評価が弱い。瑞浪駅徒歩31分の車前提エリア。長期空室・賃料下落リスク。</t>
+        </is>
+      </c>
+      <c r="E12" s="17" t="inlineStr"/>
+    </row>
+    <row r="13" ht="48" customHeight="1">
+      <c r="A13" s="31" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B13" s="31" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C13" s="32" t="inlineStr">
+        <is>
+          <t>金融機関の対応エリア</t>
+        </is>
+      </c>
+      <c r="D13" s="33" t="inlineStr">
+        <is>
+          <t>滋賀銀行が岐阜県瑞浪市・遠隔地居住者に対応可能か(営業エリア・団体扱い)を確認。</t>
+        </is>
+      </c>
+      <c r="E13" s="17" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="34" t="inlineStr">
+        <is>
+          <t>※本チェックリストは投資判断・法令適合を保証するものではありません。最終確認は金融機関・専門家(税理士・司法書士等)にご相談ください。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:A15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
